--- a/forms/trg/Formulir_TRG_naftech.xlsx
+++ b/forms/trg/Formulir_TRG_naftech.xlsx
@@ -771,7 +771,7 @@
         </is>
       </c>
       <c r="B24" s="7">
-        <f>COUNTA(Anggota!B5:B23)</f>
+        <f>COUNTA(Anggota!B5:B24)</f>
         <v/>
       </c>
     </row>
@@ -782,7 +782,7 @@
         </is>
       </c>
       <c r="B25" s="7">
-        <f>COUNTA(Anggota!F5:F23)</f>
+        <f>COUNTA(Anggota!F5:F24)</f>
         <v/>
       </c>
     </row>
@@ -808,7 +808,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M23"/>
+  <dimension ref="A1:M24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -913,20 +913,20 @@
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
-          <t>Dr. Eng. Hj. Asniawaty,ST.,MT</t>
+          <t>Prof. Dr. Ir. Zulkifli Djafar, MT</t>
         </is>
       </c>
       <c r="C5" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
-        </is>
-      </c>
-      <c r="D5" s="11" t="inlineStr">
-        <is>
-          <t>Hasanuddin University</t>
-        </is>
-      </c>
-      <c r="E5" s="11" t="n"/>
+          <t>Leader</t>
+        </is>
+      </c>
+      <c r="D5" s="12" t="n"/>
+      <c r="E5" s="11" t="inlineStr">
+        <is>
+          <t>Material Strength; Composite; Natural Fibers</t>
+        </is>
+      </c>
       <c r="F5" s="12" t="n"/>
       <c r="G5" s="12" t="n"/>
       <c r="H5" s="12" t="n"/>
@@ -935,7 +935,7 @@
       <c r="K5" s="12" t="n"/>
       <c r="L5" s="11" t="inlineStr">
         <is>
-          <t>37039440400</t>
+          <t>57211975168</t>
         </is>
       </c>
       <c r="M5" s="11" t="inlineStr">
@@ -950,12 +950,12 @@
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>Fauzan, ST., MT., Ph.D.</t>
+          <t>Dr. Eng. Hj. Asniawaty,ST.,MT</t>
         </is>
       </c>
       <c r="C6" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D6" s="11" t="inlineStr">
@@ -972,7 +972,7 @@
       <c r="K6" s="12" t="n"/>
       <c r="L6" s="11" t="inlineStr">
         <is>
-          <t>56426466100</t>
+          <t>37039440400</t>
         </is>
       </c>
       <c r="M6" s="11" t="inlineStr">
@@ -987,12 +987,12 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>Prof. Dr. Ir. H. Ilyas Renreng, MT.</t>
+          <t>Fauzan, ST., MT., Ph.D.</t>
         </is>
       </c>
       <c r="C7" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D7" s="11" t="inlineStr">
@@ -1009,7 +1009,7 @@
       <c r="K7" s="12" t="n"/>
       <c r="L7" s="11" t="inlineStr">
         <is>
-          <t>56695116100</t>
+          <t>56426466100</t>
         </is>
       </c>
       <c r="M7" s="11" t="inlineStr">
@@ -1024,17 +1024,17 @@
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>Prof. Ir. Dr. Rozli Zulkifli, (PeEng, MIEM)</t>
+          <t>Prof. Dr. Ir. H. Ilyas Renreng, MT.</t>
         </is>
       </c>
       <c r="C8" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D8" s="11" t="inlineStr">
         <is>
-          <t>University Kabangsaan Malaysia</t>
+          <t>Hasanuddin University</t>
         </is>
       </c>
       <c r="E8" s="11" t="n"/>
@@ -1046,7 +1046,7 @@
       <c r="K8" s="12" t="n"/>
       <c r="L8" s="11" t="inlineStr">
         <is>
-          <t>6507509139</t>
+          <t>56695116100</t>
         </is>
       </c>
       <c r="M8" s="11" t="inlineStr">
@@ -1061,17 +1061,17 @@
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>Massriyady Massaguni, S.ST., MT</t>
+          <t>Prof. Ir. Dr. Rozli Zulkifli, (PeEng, MIEM)</t>
         </is>
       </c>
       <c r="C9" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D9" s="11" t="inlineStr">
         <is>
-          <t>Politeknik ATI Makassar</t>
+          <t>University Kabangsaan Malaysia</t>
         </is>
       </c>
       <c r="E9" s="11" t="n"/>
@@ -1083,7 +1083,7 @@
       <c r="K9" s="12" t="n"/>
       <c r="L9" s="11" t="inlineStr">
         <is>
-          <t>59703356800</t>
+          <t>6507509139</t>
         </is>
       </c>
       <c r="M9" s="11" t="inlineStr">
@@ -1098,17 +1098,17 @@
       </c>
       <c r="B10" s="11" t="inlineStr">
         <is>
-          <t>Dr. Muhammad Yusuf Ali, ST., MT</t>
+          <t>Massriyady Massaguni, S.ST., MT</t>
         </is>
       </c>
       <c r="C10" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D10" s="11" t="inlineStr">
         <is>
-          <t>Hasanuddin University</t>
+          <t>Politeknik ATI Makassar</t>
         </is>
       </c>
       <c r="E10" s="11" t="n"/>
@@ -1118,7 +1118,11 @@
       <c r="I10" s="12" t="n"/>
       <c r="J10" s="12" t="n"/>
       <c r="K10" s="12" t="n"/>
-      <c r="L10" s="12" t="n"/>
+      <c r="L10" s="11" t="inlineStr">
+        <is>
+          <t>59703356800</t>
+        </is>
+      </c>
       <c r="M10" s="11" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -1131,12 +1135,12 @@
       </c>
       <c r="B11" s="11" t="inlineStr">
         <is>
-          <t>Muh Aswar Arham, S.ST., MT</t>
+          <t>Dr. Muhammad Yusuf Ali, ST., MT</t>
         </is>
       </c>
       <c r="C11" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D11" s="11" t="inlineStr">
@@ -1162,10 +1166,26 @@
       <c r="A12" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="B12" s="12" t="n"/>
-      <c r="C12" s="12" t="n"/>
-      <c r="D12" s="12" t="n"/>
-      <c r="E12" s="11" t="n"/>
+      <c r="B12" s="11" t="inlineStr">
+        <is>
+          <t>Muh Aswar Arham, S.ST., MT</t>
+        </is>
+      </c>
+      <c r="C12" s="11" t="inlineStr">
+        <is>
+          <t>Student</t>
+        </is>
+      </c>
+      <c r="D12" s="11" t="inlineStr">
+        <is>
+          <t>Hasanuddin University</t>
+        </is>
+      </c>
+      <c r="E12" s="11" t="inlineStr">
+        <is>
+          <t>The Natural Fiber Technology Research Group (NaFTech RG) advances sustainable materials by developing natural fiber-based composites with enhanced mechanical, thermal, and fire-resistant properties. Focusing on eco-friendly processing, surface treatments, and scalable technologies, NaFTech RG bridges academia and industry, promoting indigenous fibers for innovative applications in construction, transportation, marine, aerospace, and defense sectors.</t>
+        </is>
+      </c>
       <c r="F12" s="12" t="n"/>
       <c r="G12" s="12" t="n"/>
       <c r="H12" s="12" t="n"/>
@@ -1173,7 +1193,11 @@
       <c r="J12" s="12" t="n"/>
       <c r="K12" s="12" t="n"/>
       <c r="L12" s="12" t="n"/>
-      <c r="M12" s="12" t="n"/>
+      <c r="M12" s="11" t="inlineStr">
+        <is>
+          <t>Aktif</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="n">
@@ -1362,15 +1386,32 @@
       <c r="L23" s="12" t="n"/>
       <c r="M23" s="12" t="n"/>
     </row>
+    <row r="24">
+      <c r="A24" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="B24" s="12" t="n"/>
+      <c r="C24" s="12" t="n"/>
+      <c r="D24" s="12" t="n"/>
+      <c r="E24" s="11" t="n"/>
+      <c r="F24" s="12" t="n"/>
+      <c r="G24" s="12" t="n"/>
+      <c r="H24" s="12" t="n"/>
+      <c r="I24" s="12" t="n"/>
+      <c r="J24" s="12" t="n"/>
+      <c r="K24" s="12" t="n"/>
+      <c r="L24" s="12" t="n"/>
+      <c r="M24" s="12" t="n"/>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A2:M2"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation sqref="F5:H23" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F5:H24" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Daftar!$A$2:$A$39</formula1>
     </dataValidation>
-    <dataValidation sqref="M5:M23" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="M5:M24" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Daftar!$C$2:$C$3</formula1>
     </dataValidation>
   </dataValidations>
